--- a/Matrix.xlsx
+++ b/Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itspi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9E00252-2FD5-4E9C-993D-D2B37C912E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A7F45D-3D27-4D50-BE9D-125950D8C1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E1017569-74C7-4A26-844E-E7BAF98AD4FB}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="6">
   <si>
     <t>Unit</t>
   </si>
@@ -899,7 +899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2ABE6D3-CAB6-4577-87CC-AA7D37378D19}">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -1288,1037 +1288,911 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>602</v>
+        <v>801</v>
       </c>
       <c r="B28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
       </c>
       <c r="D28" s="1">
-        <v>525000</v>
+        <v>570000</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>603</v>
+        <v>802</v>
       </c>
       <c r="B29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
       </c>
       <c r="D29" s="1">
-        <v>510000</v>
+        <v>565000</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>604</v>
+        <v>803</v>
       </c>
       <c r="B30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
       </c>
       <c r="D30" s="1">
-        <v>540000</v>
+        <v>580000</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>605</v>
+        <v>804</v>
       </c>
       <c r="B31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C31" t="s">
         <v>4</v>
       </c>
       <c r="D31" s="1">
-        <v>535000</v>
+        <v>575000</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>701</v>
+        <v>805</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
       </c>
       <c r="D32" s="1">
-        <v>550000</v>
+        <v>555000</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>702</v>
+        <v>901</v>
       </c>
       <c r="B33">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C33" t="s">
         <v>4</v>
       </c>
       <c r="D33" s="1">
-        <v>560000</v>
+        <v>590000</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>703</v>
+        <v>902</v>
       </c>
       <c r="B34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C34" t="s">
         <v>4</v>
       </c>
       <c r="D34" s="1">
-        <v>545000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>704</v>
+        <v>903</v>
       </c>
       <c r="B35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
       </c>
       <c r="D35" s="1">
-        <v>530000</v>
+        <v>585000</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>705</v>
+        <v>904</v>
       </c>
       <c r="B36">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
       </c>
       <c r="D36" s="1">
-        <v>555000</v>
+        <v>595000</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>801</v>
+        <v>905</v>
       </c>
       <c r="B37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37" s="1">
-        <v>570000</v>
+        <v>575000</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>802</v>
+        <v>1001</v>
       </c>
       <c r="B38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D38" s="1">
-        <v>565000</v>
+        <v>610000</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>803</v>
+        <v>1002</v>
       </c>
       <c r="B39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C39" t="s">
         <v>4</v>
       </c>
       <c r="D39" s="1">
-        <v>580000</v>
+        <v>605000</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>804</v>
+        <v>1003</v>
       </c>
       <c r="B40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D40" s="1">
-        <v>575000</v>
+        <v>590000</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>805</v>
+        <v>1004</v>
       </c>
       <c r="B41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D41" s="1">
-        <v>555000</v>
+        <v>620000</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>901</v>
+        <v>1005</v>
       </c>
       <c r="B42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C42" t="s">
         <v>4</v>
       </c>
       <c r="D42" s="1">
-        <v>590000</v>
+        <v>615000</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>902</v>
+        <v>1101</v>
       </c>
       <c r="B43">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D43" s="1">
-        <v>600000</v>
+        <v>630000</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>903</v>
+        <v>1102</v>
       </c>
       <c r="B44">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C44" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D44" s="1">
-        <v>585000</v>
+        <v>640000</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>904</v>
+        <v>1103</v>
       </c>
       <c r="B45">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C45" t="s">
         <v>4</v>
       </c>
       <c r="D45" s="1">
-        <v>595000</v>
+        <v>625000</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>905</v>
+        <v>1104</v>
       </c>
       <c r="B46">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
       </c>
       <c r="D46" s="1">
-        <v>575000</v>
+        <v>610000</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>1001</v>
+        <v>1105</v>
       </c>
       <c r="B47">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C47" t="s">
         <v>4</v>
       </c>
       <c r="D47" s="1">
-        <v>610000</v>
+        <v>635000</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>1002</v>
+        <v>1201</v>
       </c>
       <c r="B48">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
         <v>4</v>
       </c>
       <c r="D48" s="1">
-        <v>605000</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>1003</v>
+        <v>1202</v>
       </c>
       <c r="B49">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C49" t="s">
         <v>5</v>
       </c>
       <c r="D49" s="1">
-        <v>590000</v>
+        <v>645000</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>1004</v>
+        <v>1203</v>
       </c>
       <c r="B50">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
         <v>4</v>
       </c>
       <c r="D50" s="1">
-        <v>620000</v>
+        <v>660000</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>1005</v>
+        <v>1204</v>
       </c>
       <c r="B51">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
         <v>4</v>
       </c>
       <c r="D51" s="1">
-        <v>615000</v>
+        <v>655000</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>1101</v>
+        <v>1205</v>
       </c>
       <c r="B52">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C52" t="s">
         <v>5</v>
       </c>
       <c r="D52" s="1">
-        <v>630000</v>
+        <v>635000</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>1102</v>
+        <v>1301</v>
       </c>
       <c r="B53">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
         <v>4</v>
       </c>
       <c r="D53" s="1">
-        <v>640000</v>
+        <v>670000</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>1103</v>
+        <v>1302</v>
       </c>
       <c r="B54">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
         <v>4</v>
       </c>
       <c r="D54" s="1">
-        <v>625000</v>
+        <v>680000</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>1104</v>
+        <v>1303</v>
       </c>
       <c r="B55">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
         <v>5</v>
       </c>
       <c r="D55" s="1">
-        <v>610000</v>
+        <v>665000</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>1105</v>
+        <v>1304</v>
       </c>
       <c r="B56">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C56" t="s">
         <v>4</v>
       </c>
       <c r="D56" s="1">
-        <v>635000</v>
+        <v>675000</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>1201</v>
+        <v>1305</v>
       </c>
       <c r="B57">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D57" s="1">
-        <v>650000</v>
+        <v>655000</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>1202</v>
+        <v>1401</v>
       </c>
       <c r="B58">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C58" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D58" s="1">
-        <v>645000</v>
+        <v>690000</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>1203</v>
+        <v>1402</v>
       </c>
       <c r="B59">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C59" t="s">
         <v>4</v>
       </c>
       <c r="D59" s="1">
-        <v>660000</v>
+        <v>685000</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>1204</v>
+        <v>1403</v>
       </c>
       <c r="B60">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C60" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D60" s="1">
-        <v>655000</v>
+        <v>670000</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>1205</v>
+        <v>1404</v>
       </c>
       <c r="B61">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C61" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D61" s="1">
-        <v>635000</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>1301</v>
+        <v>1405</v>
       </c>
       <c r="B62">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C62" t="s">
         <v>4</v>
       </c>
       <c r="D62" s="1">
-        <v>670000</v>
+        <v>695000</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>1302</v>
+        <v>1501</v>
       </c>
       <c r="B63">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C63" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D63" s="1">
-        <v>680000</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>1303</v>
+        <v>1502</v>
       </c>
       <c r="B64">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C64" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D64" s="1">
-        <v>665000</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>1304</v>
+        <v>1503</v>
       </c>
       <c r="B65">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C65" t="s">
         <v>4</v>
       </c>
       <c r="D65" s="1">
-        <v>675000</v>
+        <v>705000</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>1305</v>
+        <v>1504</v>
       </c>
       <c r="B66">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
       </c>
       <c r="D66" s="1">
-        <v>655000</v>
+        <v>690000</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>1401</v>
+        <v>1505</v>
       </c>
       <c r="B67">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C67" t="s">
         <v>4</v>
       </c>
       <c r="D67" s="1">
-        <v>690000</v>
+        <v>715000</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>1402</v>
+        <v>1601</v>
       </c>
       <c r="B68">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C68" t="s">
         <v>4</v>
       </c>
       <c r="D68" s="1">
-        <v>685000</v>
+        <v>730000</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>1403</v>
+        <v>1602</v>
       </c>
       <c r="B69">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C69" t="s">
         <v>5</v>
       </c>
       <c r="D69" s="1">
-        <v>670000</v>
+        <v>725000</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>1404</v>
+        <v>1603</v>
       </c>
       <c r="B70">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C70" t="s">
         <v>4</v>
       </c>
       <c r="D70" s="1">
-        <v>700000</v>
+        <v>740000</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>1405</v>
+        <v>1604</v>
       </c>
       <c r="B71">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C71" t="s">
         <v>4</v>
       </c>
       <c r="D71" s="1">
-        <v>695000</v>
+        <v>735000</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>1501</v>
+        <v>1605</v>
       </c>
       <c r="B72">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C72" t="s">
         <v>5</v>
       </c>
       <c r="D72" s="1">
-        <v>710000</v>
+        <v>715000</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>1502</v>
+        <v>1701</v>
       </c>
       <c r="B73">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C73" t="s">
         <v>4</v>
       </c>
       <c r="D73" s="1">
-        <v>720000</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>1503</v>
+        <v>1702</v>
       </c>
       <c r="B74">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C74" t="s">
         <v>4</v>
       </c>
       <c r="D74" s="1">
-        <v>705000</v>
+        <v>760000</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>1504</v>
+        <v>1703</v>
       </c>
       <c r="B75">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C75" t="s">
         <v>5</v>
       </c>
       <c r="D75" s="1">
-        <v>690000</v>
+        <v>745000</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>1505</v>
+        <v>1704</v>
       </c>
       <c r="B76">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C76" t="s">
         <v>4</v>
       </c>
       <c r="D76" s="1">
-        <v>715000</v>
+        <v>755000</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>1601</v>
+        <v>1705</v>
       </c>
       <c r="B77">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C77" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D77" s="1">
-        <v>730000</v>
+        <v>735000</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>1602</v>
+        <v>1801</v>
       </c>
       <c r="B78">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C78" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D78" s="1">
-        <v>725000</v>
+        <v>770000</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>1603</v>
+        <v>1802</v>
       </c>
       <c r="B79">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C79" t="s">
         <v>4</v>
       </c>
       <c r="D79" s="1">
-        <v>740000</v>
+        <v>765000</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>1604</v>
+        <v>1803</v>
       </c>
       <c r="B80">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C80" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D80" s="1">
-        <v>735000</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>1605</v>
+        <v>1804</v>
       </c>
       <c r="B81">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C81" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D81" s="1">
-        <v>715000</v>
+        <v>780000</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>1701</v>
+        <v>1805</v>
       </c>
       <c r="B82">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C82" t="s">
         <v>4</v>
       </c>
       <c r="D82" s="1">
-        <v>750000</v>
+        <v>775000</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>1702</v>
+        <v>1901</v>
       </c>
       <c r="B83">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C83" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D83" s="1">
-        <v>760000</v>
+        <v>790000</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>1703</v>
+        <v>1902</v>
       </c>
       <c r="B84">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C84" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D84" s="1">
-        <v>745000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>1704</v>
+        <v>1903</v>
       </c>
       <c r="B85">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C85" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="1">
-        <v>755000</v>
+        <v>785000</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>1705</v>
+        <v>1904</v>
       </c>
       <c r="B86">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C86" t="s">
         <v>5</v>
       </c>
       <c r="D86" s="1">
-        <v>735000</v>
+        <v>770000</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>1801</v>
+        <v>1905</v>
       </c>
       <c r="B87">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C87" t="s">
         <v>4</v>
       </c>
       <c r="D87" s="1">
-        <v>770000</v>
+        <v>795000</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>1802</v>
+        <v>2001</v>
       </c>
       <c r="B88">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C88" t="s">
         <v>4</v>
       </c>
       <c r="D88" s="1">
-        <v>765000</v>
+        <v>810000</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>1803</v>
+        <v>2002</v>
       </c>
       <c r="B89">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C89" t="s">
         <v>5</v>
       </c>
       <c r="D89" s="1">
-        <v>750000</v>
+        <v>805000</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>1804</v>
+        <v>2003</v>
       </c>
       <c r="B90">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C90" t="s">
         <v>4</v>
       </c>
       <c r="D90" s="1">
-        <v>780000</v>
+        <v>820000</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>1805</v>
+        <v>2004</v>
       </c>
       <c r="B91">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C91" t="s">
         <v>4</v>
       </c>
       <c r="D91" s="1">
-        <v>775000</v>
+        <v>815000</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>1901</v>
+        <v>2005</v>
       </c>
       <c r="B92">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C92" t="s">
         <v>5</v>
       </c>
       <c r="D92" s="1">
-        <v>790000</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93">
-        <v>1902</v>
-      </c>
-      <c r="B93">
-        <v>19</v>
-      </c>
-      <c r="C93" t="s">
-        <v>4</v>
-      </c>
-      <c r="D93" s="1">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94">
-        <v>1903</v>
-      </c>
-      <c r="B94">
-        <v>19</v>
-      </c>
-      <c r="C94" t="s">
-        <v>4</v>
-      </c>
-      <c r="D94" s="1">
-        <v>785000</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95">
-        <v>1904</v>
-      </c>
-      <c r="B95">
-        <v>19</v>
-      </c>
-      <c r="C95" t="s">
-        <v>5</v>
-      </c>
-      <c r="D95" s="1">
-        <v>770000</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96">
-        <v>1905</v>
-      </c>
-      <c r="B96">
-        <v>19</v>
-      </c>
-      <c r="C96" t="s">
-        <v>4</v>
-      </c>
-      <c r="D96" s="1">
-        <v>795000</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97">
-        <v>2001</v>
-      </c>
-      <c r="B97">
-        <v>20</v>
-      </c>
-      <c r="C97" t="s">
-        <v>4</v>
-      </c>
-      <c r="D97" s="1">
-        <v>810000</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98">
-        <v>2002</v>
-      </c>
-      <c r="B98">
-        <v>20</v>
-      </c>
-      <c r="C98" t="s">
-        <v>5</v>
-      </c>
-      <c r="D98" s="1">
-        <v>805000</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99">
-        <v>2003</v>
-      </c>
-      <c r="B99">
-        <v>20</v>
-      </c>
-      <c r="C99" t="s">
-        <v>4</v>
-      </c>
-      <c r="D99" s="1">
-        <v>820000</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100">
-        <v>2004</v>
-      </c>
-      <c r="B100">
-        <v>20</v>
-      </c>
-      <c r="C100" t="s">
-        <v>4</v>
-      </c>
-      <c r="D100" s="1">
-        <v>815000</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101">
-        <v>2005</v>
-      </c>
-      <c r="B101">
-        <v>20</v>
-      </c>
-      <c r="C101" t="s">
-        <v>5</v>
-      </c>
-      <c r="D101" s="1">
         <v>795000</v>
       </c>
     </row>
